--- a/src/main/resources/static/docs/Usuarios_prueba.xlsx
+++ b/src/main/resources/static/docs/Usuarios_prueba.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UNED\DESARROLLOWEB\ped-2026\uned-aplicacionweb\src\main\resources\static\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\prueba\uned-aplicacionweb\src\main\resources\static\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{92143FE8-6C0C-4E73-A511-641A0E1302E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE8B2C1-3CD3-4C62-87AD-7FA225658CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15360" windowHeight="10920" xr2:uid="{568DB4F4-389A-42A8-B0F3-22C0D84B2A08}"/>
+    <workbookView xWindow="3495" yWindow="2895" windowWidth="18450" windowHeight="10800" xr2:uid="{568DB4F4-389A-42A8-B0F3-22C0D84B2A08}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -39,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
   <si>
     <t>USUARIOS GENERADOS PARA PRUEBAS</t>
   </si>
@@ -147,13 +145,16 @@
   </si>
   <si>
     <t>Wilson</t>
+  </si>
+  <si>
+    <t>ESTUD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -175,9 +176,14 @@
       <family val="3"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
+      <sz val="14"/>
+      <color rgb="FF2A00FF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -200,20 +206,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -544,23 +549,23 @@
   <dimension ref="B2:H12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="3" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="40.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.85546875" customWidth="1"/>
-    <col min="5" max="5" width="16.5703125" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.140625" customWidth="1"/>
     <col min="7" max="7" width="21.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
@@ -582,136 +587,144 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
+    <row r="5" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="2" t="s">
+    <row r="7" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="2" t="s">
+    <row r="8" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E8" t="s">
+      <c r="D8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="2" t="s">
+    <row r="9" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E9" t="s">
+      <c r="D9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="2" t="s">
+    <row r="10" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E10" t="s">
+      <c r="D10" s="3"/>
+      <c r="E10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="2" t="s">
+    <row r="11" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E11" t="s">
+      <c r="D11" s="3"/>
+      <c r="E11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="12" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="2"/>
+      <c r="B12" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -719,11 +732,13 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C8" r:id="rId1" xr:uid="{BD44FBD0-A293-42B4-A6A3-C39F335DE5DE}"/>
+    <hyperlink ref="B9" r:id="rId2" xr:uid="{10437B6C-4041-47C8-BF94-2F9AA8D36254}"/>
+    <hyperlink ref="B10" r:id="rId3" xr:uid="{B25EC0F1-FEBA-40E8-8C4E-AC0A68624102}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>
--- a/src/main/resources/static/docs/Usuarios_prueba.xlsx
+++ b/src/main/resources/static/docs/Usuarios_prueba.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\prueba\uned-aplicacionweb\src\main\resources\static\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE8B2C1-3CD3-4C62-87AD-7FA225658CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F544091-578C-4818-9E72-9455743916A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3495" yWindow="2895" windowWidth="18450" windowHeight="10800" xr2:uid="{568DB4F4-389A-42A8-B0F3-22C0D84B2A08}"/>
+    <workbookView xWindow="15" yWindow="1110" windowWidth="22530" windowHeight="10260" xr2:uid="{568DB4F4-389A-42A8-B0F3-22C0D84B2A08}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="37">
   <si>
     <t>USUARIOS GENERADOS PARA PRUEBAS</t>
   </si>
@@ -184,9 +184,8 @@
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -588,13 +587,13 @@
       </c>
     </row>
     <row r="5" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="4" t="s">
@@ -608,13 +607,13 @@
       </c>
     </row>
     <row r="6" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E6" s="4" t="s">
@@ -628,98 +627,102 @@
       </c>
     </row>
     <row r="7" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>21</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="4" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>24</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3" t="s">
+      <c r="D10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="4" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="11" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3" t="s">
+      <c r="D11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="4" t="s">
         <v>32</v>
       </c>
     </row>
